--- a/Testes/reescala/Teste seleção e cruzamento/Teste3/3_melhor_escala.xlsx
+++ b/Testes/reescala/Teste seleção e cruzamento/Teste3/3_melhor_escala.xlsx
@@ -793,8 +793,8 @@
       <c r="AH2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI2" s="5" t="n">
-        <v>0</v>
+      <c r="AI2" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -901,8 +901,8 @@
       <c r="AG3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" s="4" t="n">
-        <v>1</v>
+      <c r="AH3" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI3" s="5" t="n">
         <v>0</v>
@@ -1012,11 +1012,11 @@
       <c r="AG4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="4" t="n">
-        <v>1</v>
+      <c r="AH4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1048,11 +1048,11 @@
       <c r="H5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>1</v>
+      <c r="I5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>0</v>
@@ -1069,17 +1069,17 @@
       <c r="O5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>1</v>
+      <c r="P5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="T5" s="5" t="n">
         <v>0</v>
@@ -1111,11 +1111,11 @@
       <c r="AC5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="4" t="n">
-        <v>1</v>
+      <c r="AD5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AF5" s="5" t="n">
         <v>0</v>
@@ -1186,14 +1186,14 @@
       <c r="Q6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" s="5" t="n">
-        <v>0</v>
+      <c r="R6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="U6" s="5" t="n">
         <v>0</v>
@@ -1288,11 +1288,11 @@
       <c r="N7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="4" t="n">
-        <v>1</v>
+      <c r="O7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1405,8 +1405,8 @@
       <c r="P8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="4" t="n">
-        <v>1</v>
+      <c r="Q8" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R8" s="5" t="n">
         <v>0</v>
@@ -1441,14 +1441,14 @@
       <c r="AB8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AC8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE8" s="5" t="n">
-        <v>0</v>
+      <c r="AC8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AF8" s="5" t="n">
         <v>0</v>
@@ -1549,14 +1549,14 @@
       <c r="AA9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AB9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="4" t="n">
-        <v>1</v>
+      <c r="AB9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AE9" s="5" t="n">
         <v>0</v>
@@ -1627,17 +1627,17 @@
       <c r="P10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="4" t="n">
-        <v>1</v>
+      <c r="Q10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="U10" s="5" t="n">
         <v>0</v>
@@ -1705,11 +1705,11 @@
       <c r="E11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>0</v>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>0</v>
@@ -1738,8 +1738,8 @@
       <c r="P11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" s="5" t="n">
-        <v>0</v>
+      <c r="Q11" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R11" s="4" t="n">
         <v>1</v>
@@ -1747,11 +1747,11 @@
       <c r="S11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" s="5" t="n">
-        <v>0</v>
+      <c r="T11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="V11" s="5" t="n">
         <v>0</v>
@@ -1780,11 +1780,11 @@
       <c r="AD11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AE11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" s="5" t="n">
-        <v>0</v>
+      <c r="AE11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AG11" s="5" t="n">
         <v>0</v>
@@ -1849,32 +1849,32 @@
       <c r="P12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" s="4" t="n">
-        <v>1</v>
+      <c r="Q12" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="5" t="n">
-        <v>0</v>
+      <c r="S12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="Z12" s="5" t="n">
         <v>0</v>
@@ -1948,11 +1948,11 @@
       <c r="L13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>0</v>
+      <c r="M13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="O13" s="5" t="n">
         <v>0</v>
@@ -1960,8 +1960,8 @@
       <c r="P13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" s="5" t="n">
-        <v>0</v>
+      <c r="Q13" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R13" s="4" t="n">
         <v>1</v>
@@ -2113,20 +2113,20 @@
       <c r="AD14" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AE14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI14" s="5" t="n">
-        <v>0</v>
+      <c r="AE14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2158,11 +2158,11 @@
       <c r="H15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>1</v>
+      <c r="I15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K15" s="5" t="n">
         <v>0</v>
@@ -2191,11 +2191,11 @@
       <c r="S15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" s="5" t="n">
-        <v>0</v>
+      <c r="T15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="V15" s="5" t="n">
         <v>0</v>
@@ -2323,11 +2323,11 @@
       <c r="Z16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AA16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="4" t="n">
-        <v>1</v>
+      <c r="AA16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AC16" s="5" t="n">
         <v>0</v>
@@ -2437,11 +2437,11 @@
       <c r="AA17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AB17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="4" t="n">
-        <v>1</v>
+      <c r="AB17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AD17" s="5" t="n">
         <v>0</v>
@@ -2566,11 +2566,11 @@
       <c r="AG18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" s="4" t="n">
-        <v>1</v>
+      <c r="AH18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI18" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2602,14 +2602,14 @@
       <c r="H19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>0</v>
+      <c r="I19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="L19" s="5" t="n">
         <v>0</v>
@@ -2626,8 +2626,8 @@
       <c r="P19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="4" t="n">
-        <v>1</v>
+      <c r="Q19" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R19" s="5" t="n">
         <v>0</v>
@@ -2719,26 +2719,26 @@
       <c r="J20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="5" t="n">
-        <v>0</v>
+      <c r="K20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R20" s="5" t="n">
         <v>0</v>
@@ -2956,11 +2956,11 @@
       <c r="O22" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="5" t="n">
-        <v>0</v>
+      <c r="P22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R22" s="5" t="n">
         <v>0</v>
@@ -3037,11 +3037,11 @@
       <c r="E23" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>1</v>
+      <c r="F23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0</v>
@@ -3112,11 +3112,11 @@
       <c r="AD23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AE23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="4" t="n">
-        <v>1</v>
+      <c r="AE23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AG23" s="5" t="n">
         <v>0</v>
@@ -3187,14 +3187,14 @@
       <c r="R24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" s="5" t="n">
-        <v>0</v>
+      <c r="S24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="V24" s="5" t="n">
         <v>0</v>
@@ -3223,11 +3223,11 @@
       <c r="AD24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AE24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="4" t="n">
-        <v>1</v>
+      <c r="AE24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AG24" s="5" t="n">
         <v>0</v>
@@ -3262,11 +3262,11 @@
       <c r="F25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>1</v>
+      <c r="G25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>0</v>
@@ -3373,17 +3373,17 @@
       <c r="F26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>1</v>
+      <c r="G26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>0</v>
@@ -3442,17 +3442,17 @@
       <c r="AC26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG26" s="5" t="n">
-        <v>0</v>
+      <c r="AD26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AH26" s="5" t="n">
         <v>0</v>
@@ -3514,8 +3514,8 @@
       <c r="P27" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" s="5" t="n">
-        <v>0</v>
+      <c r="Q27" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R27" s="4" t="n">
         <v>1</v>
@@ -3529,14 +3529,14 @@
       <c r="U27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X27" s="5" t="n">
-        <v>0</v>
+      <c r="V27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="Y27" s="5" t="n">
         <v>0</v>
@@ -3553,17 +3553,17 @@
       <c r="AC27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="4" t="n">
-        <v>1</v>
+      <c r="AD27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AH27" s="5" t="n">
         <v>0</v>
@@ -3709,17 +3709,17 @@
       <c r="G29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>1</v>
+      <c r="H29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="L29" s="5" t="n">
         <v>0</v>
@@ -3742,11 +3742,11 @@
       <c r="R29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="4" t="n">
-        <v>1</v>
+      <c r="S29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="U29" s="5" t="n">
         <v>0</v>
@@ -3757,17 +3757,17 @@
       <c r="W29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="X29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA29" s="5" t="n">
-        <v>0</v>
+      <c r="X29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AB29" s="5" t="n">
         <v>0</v>
@@ -3814,26 +3814,26 @@
       <c r="E30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>0</v>
+      <c r="F30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="M30" s="5" t="n">
         <v>0</v>
@@ -3856,14 +3856,14 @@
       <c r="S30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>1</v>
+      <c r="T30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="W30" s="5" t="n">
         <v>0</v>
@@ -3970,14 +3970,14 @@
       <c r="T31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" s="4" t="n">
-        <v>1</v>
+      <c r="U31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="X31" s="5" t="n">
         <v>0</v>
@@ -3994,26 +3994,26 @@
       <c r="AB31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AC31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI31" s="5" t="n">
-        <v>0</v>
+      <c r="AC31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -4042,23 +4042,23 @@
       <c r="G32" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v>0</v>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="N32" s="5" t="n">
         <v>0</v>
@@ -4075,11 +4075,11 @@
       <c r="R32" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="4" t="n">
-        <v>1</v>
+      <c r="S32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="U32" s="5" t="n">
         <v>0</v>
@@ -4096,23 +4096,23 @@
       <c r="Y32" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Z32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="4" t="n">
-        <v>1</v>
+      <c r="Z32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE32" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AF32" s="5" t="n">
         <v>0</v>
@@ -4150,23 +4150,23 @@
       <c r="F33" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>0</v>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="M33" s="5" t="n">
         <v>0</v>
@@ -4180,8 +4180,8 @@
       <c r="P33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" s="5" t="n">
-        <v>0</v>
+      <c r="Q33" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R33" s="4" t="n">
         <v>1</v>
@@ -4342,11 +4342,11 @@
       <c r="AG34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI34" s="5" t="n">
-        <v>0</v>
+      <c r="AH34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -4375,20 +4375,20 @@
       <c r="G35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v>0</v>
+      <c r="H35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="M35" s="5" t="n">
         <v>0</v>
@@ -4411,11 +4411,11 @@
       <c r="S35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U35" s="5" t="n">
-        <v>0</v>
+      <c r="T35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="V35" s="5" t="n">
         <v>0</v>
@@ -4501,11 +4501,11 @@
       <c r="L36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="4" t="n">
-        <v>1</v>
+      <c r="M36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="O36" s="5" t="n">
         <v>0</v>
@@ -4513,8 +4513,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -4522,17 +4522,17 @@
       <c r="S36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W36" s="5" t="n">
-        <v>0</v>
+      <c r="T36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="X36" s="5" t="n">
         <v>0</v>
@@ -4561,11 +4561,11 @@
       <c r="AF36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH36" s="5" t="n">
-        <v>0</v>
+      <c r="AG36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI36" s="5" t="n">
         <v>0</v>
@@ -4633,32 +4633,32 @@
       <c r="S37" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB37" s="5" t="n">
-        <v>0</v>
+      <c r="T37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AC37" s="5" t="n">
         <v>0</v>
@@ -4744,29 +4744,29 @@
       <c r="S38" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA38" s="5" t="n">
-        <v>0</v>
+      <c r="T38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AB38" s="5" t="n">
         <v>0</v>
@@ -4819,11 +4819,11 @@
       <c r="G39" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>0</v>
+      <c r="H39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="J39" s="5" t="n">
         <v>0</v>
@@ -4891,17 +4891,17 @@
       <c r="AE39" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AF39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" s="4" t="n">
-        <v>1</v>
+      <c r="AF39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI39" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -4927,20 +4927,20 @@
       <c r="F40" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="4" t="n">
-        <v>1</v>
+      <c r="G40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="L40" s="5" t="n">
         <v>0</v>
@@ -5041,32 +5041,32 @@
       <c r="G41" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v>1</v>
+      <c r="H41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P41" s="5" t="n">
-        <v>0</v>
+      <c r="N41" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="Q41" s="4" t="n">
         <v>1</v>
@@ -5158,14 +5158,14 @@
       <c r="I42" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>0</v>
+      <c r="J42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="M42" s="5" t="n">
         <v>0</v>
@@ -5188,29 +5188,29 @@
       <c r="S42" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA42" s="5" t="n">
-        <v>0</v>
+      <c r="T42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AB42" s="5" t="n">
         <v>0</v>
@@ -5227,14 +5227,14 @@
       <c r="AF42" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG42" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI42" s="5" t="n">
-        <v>0</v>
+      <c r="AG42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -5272,14 +5272,14 @@
       <c r="J43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="K43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M43" s="5" t="n">
-        <v>0</v>
+      <c r="K43" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="N43" s="5" t="n">
         <v>0</v>
@@ -5290,8 +5290,8 @@
       <c r="P43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" s="4" t="n">
-        <v>1</v>
+      <c r="Q43" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R43" s="5" t="n">
         <v>0</v>
@@ -5509,23 +5509,23 @@
       <c r="O45" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" s="4" t="n">
-        <v>1</v>
+      <c r="P45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="V45" s="5" t="n">
         <v>0</v>
@@ -5536,11 +5536,11 @@
       <c r="X45" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z45" s="5" t="n">
-        <v>0</v>
+      <c r="Y45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="5" t="n">
         <v>0</v>
@@ -5614,11 +5614,11 @@
       <c r="M46" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="4" t="n">
-        <v>1</v>
+      <c r="N46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P46" s="5" t="n">
         <v>0</v>
@@ -5710,11 +5710,11 @@
       <c r="H47" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="5" t="n">
-        <v>0</v>
+      <c r="I47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="K47" s="5" t="n">
         <v>0</v>
@@ -5725,11 +5725,11 @@
       <c r="M47" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="N47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="4" t="n">
-        <v>1</v>
+      <c r="N47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P47" s="5" t="n">
         <v>0</v>
@@ -5746,47 +5746,47 @@
       <c r="T47" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH47" s="5" t="n">
-        <v>0</v>
+      <c r="U47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI47" s="5" t="n">
         <v>0</v>
@@ -5860,11 +5860,11 @@
       <c r="U48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W48" s="5" t="n">
-        <v>0</v>
+      <c r="V48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="X48" s="5" t="n">
         <v>0</v>
@@ -5896,11 +5896,11 @@
       <c r="AG48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" s="4" t="n">
-        <v>1</v>
+      <c r="AH48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI48" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -5929,32 +5929,32 @@
       <c r="G49" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="4" t="n">
-        <v>1</v>
+      <c r="H49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="L49" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="M49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="4" t="n">
-        <v>1</v>
+      <c r="M49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Q49" s="5" t="n">
         <v>0</v>
@@ -5983,20 +5983,20 @@
       <c r="Y49" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" s="4" t="n">
-        <v>1</v>
+      <c r="Z49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD49" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AE49" s="5" t="n">
         <v>0</v>
@@ -6034,23 +6034,23 @@
       <c r="E50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>0</v>
+      <c r="F50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="L50" s="5" t="n">
         <v>0</v>
@@ -6079,11 +6079,11 @@
       <c r="T50" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V50" s="5" t="n">
-        <v>0</v>
+      <c r="U50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="W50" s="5" t="n">
         <v>0</v>
@@ -6163,11 +6163,11 @@
       <c r="K51" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="L51" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v>0</v>
+      <c r="L51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="N51" s="5" t="n">
         <v>0</v>
@@ -6232,8 +6232,8 @@
       <c r="AH51" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI51" s="4" t="n">
-        <v>1</v>
+      <c r="AI51" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -6301,23 +6301,23 @@
       <c r="T52" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="U52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z52" s="5" t="n">
-        <v>0</v>
+      <c r="U52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="5" t="n">
         <v>0</v>
@@ -6328,14 +6328,14 @@
       <c r="AC52" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF52" s="5" t="n">
-        <v>0</v>
+      <c r="AD52" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AG52" s="5" t="n">
         <v>0</v>
